--- a/public/templates/Litmus_Bulk_Import_Master_Template.xlsx
+++ b/public/templates/Litmus_Bulk_Import_Master_Template.xlsx
@@ -519,7 +519,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Must have unique names. Categories must be created first before mapping tests to them.</t>
+          <t>Must have unique names. Categories can optionally include comma-separated subcategories.</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Parameters syntax: 'Name:Unit:MinLimit:MaxLimit:Price'. Multiple parameters separated by semicolon ';'. Base price is auto-calculated.</t>
+          <t>Parameters syntax: 'Name:Unit:MinLimit:MaxLimit:Price'. Multiple parameters separated by semicolon ';'. Subcategories are comma-separated.</t>
         </is>
       </c>
     </row>
@@ -636,18 +636,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="86" customWidth="1" min="1" max="1"/>
-    <col width="117" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="111" customWidth="1" min="1" max="1"/>
+    <col width="93" customWidth="1" min="2" max="2"/>
+    <col width="117" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Fill Category names and descriptions. Category names must be unique.</t>
+          <t>INSTRUCTIONS: Fill Category names, optional subcategories, and descriptions. Category names must be unique.</t>
         </is>
       </c>
     </row>
@@ -659,10 +660,15 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>subcategories</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>imageUrl</t>
         </is>
@@ -684,6 +690,11 @@
           <t>OPTIONAL</t>
         </is>
       </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -693,10 +704,15 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
+          <t>Raw Milk, Pasteurized Milk, Cheese &amp; Paneer, Butter &amp; Ghee, Yogurt &amp; Curd, Ice Cream</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
           <t>Safety, quality, and nutritional analysis for raw milk, pasteurized milk, cheese, butter, paneer, and ice creams.</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>https://example.com/images/dairy.png</t>
         </is>
@@ -710,10 +726,15 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
+          <t>Packaged Drinking Water, Carbonated Beverages, Fruit Juices &amp; Squashes, Tea &amp; Coffee</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
           <t>Physicochemical and microbial profiling for packaged water, fruit juices, carbonated drinks, tea, and coffee.</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -723,10 +744,15 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
+          <t>Bread &amp; Buns, Biscuits &amp; Cookies, Cakes &amp; Pastries, Chocolates &amp; Candies</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
           <t>Testing for flour quality, moisture, preservatives, sugar profile, and shelf-life analysis for baked goods.</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -736,10 +762,15 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
+          <t>Fresh Raw Meat, Processed Meat &amp; Sausages, Poultry &amp; Eggs, Fish &amp; Shellfish</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
           <t>Veterinary drug residue, heavy metals, microbial safety (Salmonella, Listeria), and freshness parameters.</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -749,14 +780,19 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
+          <t>Edible Vegetable Oils, Hydrogenated Fats (Vanaspati), Olive &amp; Specialty Oils, Animal Fats</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
           <t>Fatty acid profiling, Rancidity, Peroxide value, Free Fatty Acids (FFA), and adulteration screening.</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -768,10 +804,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="123" customWidth="1" min="1" max="1"/>
+    <col width="139" customWidth="1" min="1" max="1"/>
     <col width="101" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
@@ -781,16 +817,17 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="121" customWidth="1" min="14" max="14"/>
+    <col width="94" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Define test details and parameters. Use 'Name:Unit:Min:Max:Price' format for parameters separated by ';'.</t>
+          <t>INSTRUCTIONS: Define test details, subcategories, and parameters. Use 'Name:Unit:Min:Max:Price' format for parameters separated by ';'.</t>
         </is>
       </c>
     </row>
@@ -847,20 +884,25 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
+          <t>applicableSubcategories</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
           <t>isPopular</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>discountType</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>discountValue</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>parameters</t>
         </is>
@@ -932,7 +974,12 @@
           <t>OPTIONAL</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>REQUIRED *</t>
         </is>
@@ -987,18 +1034,23 @@
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
+          <t>Raw Milk, Pasteurized Milk</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>PERCENTAGE</t>
         </is>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="N4" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>Total Fat:%:3.0:8.0:180; Solids Not Fat (SNF):%:8.0:10.5:120; Density:g/ml:1.026:1.032:100</t>
         </is>
@@ -1007,28 +1059,28 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Microbial Safety Screen (E. Coli &amp; Coliforms)</t>
+          <t>Cheese &amp; Paneer Moisture &amp; Fat Panel</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Quantitative enumeration of total viable coliforms and Escherichia coli in food &amp; water matrices.</t>
+          <t>Determination of moisture and fat on dry basis for cheese, paneer, and cottage cheese.</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>IS:5401 (Part 1):2012 / ISO 4832:2006</t>
+          <t>IS:2785 - 1979 / FSSAI Manual 01</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>48 Hours</t>
+          <t>24 Hours</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -1039,54 +1091,63 @@
       <c r="H5" s="9" t="inlineStr"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Dairy &amp; Milk Products</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Cheese &amp; Paneer</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="N5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>Total Coliform Count:cfu/g:0:10:350; E. Coli Count:cfu/g:0:0:450</t>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>Moisture Content:%:0:60.0:250; Fat on Dry Basis:%:45.0:70.0:300</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Heavy Metals Residue Panel</t>
+          <t>Microbial Safety Screen (E. Coli &amp; Coliforms)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Inductively Coupled Plasma Mass Spectrometry (ICP-MS) detection for toxic heavy metals.</t>
+          <t>Quantitative enumeration of total viable coliforms and Escherichia coli in food &amp; water matrices.</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr"/>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>AOAC 2015.01 / FSSAI Manual 02</t>
+          <t>IS:5401 (Part 1):2012 / ISO 4832:2006</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>72 Hours</t>
+          <t>48 Hours</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -1101,20 +1162,79 @@
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>Total Coliform Count:cfu/g:0:10:350; E. Coli Count:cfu/g:0:0:450</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Heavy Metals Residue Panel</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Inductively Coupled Plasma Mass Spectrometry (ICP-MS) detection for toxic heavy metals.</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>AOAC 2015.01 / FSSAI Manual 02</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Chemical</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>72 Hours</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>FLAT</t>
         </is>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M7" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>Lead (Pb):ppm:0.0:0.1:400; Cadmium (Cd):ppm:0.0:0.05:400; Arsenic (As):ppm:0.0:0.1:450; Mercury (Hg):ppm:0.0:0.01:450</t>
         </is>
@@ -1122,7 +1242,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1135,7 +1255,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="123" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -1405,7 +1525,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>

--- a/public/templates/Litmus_Bulk_Import_Master_Template.xlsx
+++ b/public/templates/Litmus_Bulk_Import_Master_Template.xlsx
@@ -804,24 +804,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="139" customWidth="1" min="1" max="1"/>
-    <col width="101" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="101" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="121" customWidth="1" min="14" max="14"/>
-    <col width="94" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="121" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -839,70 +841,80 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>discountType</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>discountValue</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>offerPrice</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>turnAroundTime</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>testType</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>fssaiMethod</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>imageUrl</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>fssaiMethod</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>testType</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>turnAroundTime</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>creatorType</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>labName</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>isApplicableToAll</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>applicableCategories</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>applicableSubcategories</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>isPopular</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>discountType</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>discountValue</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>parameters</t>
         </is>
@@ -914,9 +926,9 @@
           <t>REQUIRED *</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>OPTIONAL</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>REQUIRED *</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -979,9 +991,19 @@
           <t>OPTIONAL</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>REQUIRED *</t>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
         </is>
       </c>
     </row>
@@ -991,66 +1013,72 @@
           <t>Milk Fat &amp; Solids Analysis</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>24 Hours</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Chemical</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>IS:1479 (Part I) - 1960</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Complete determination of milk fat by Gerber method and solids-not-fat (SNF) calculation.</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>https://example.com/icons/milk-fat.png</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>IS:1479 (Part I) - 1960</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>24 Hours</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr"/>
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>Dairy &amp; Milk Products</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>Raw Milk, Pasteurized Milk</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="P4" s="9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>PERCENTAGE</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="Q4" s="9" t="inlineStr">
         <is>
           <t>Total Fat:%:3.0:8.0:180; Solids Not Fat (SNF):%:8.0:10.5:120; Density:g/ml:1.026:1.032:100</t>
         </is>
@@ -1062,62 +1090,68 @@
           <t>Cheese &amp; Paneer Moisture &amp; Fat Panel</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="9" t="n">
+        <v>550</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>550</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>24 Hours</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Chemical</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>IS:2785 - 1979 / FSSAI Manual 01</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Determination of moisture and fat on dry basis for cheese, paneer, and cottage cheese.</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr"/>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>IS:2785 - 1979 / FSSAI Manual 01</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>24 Hours</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr"/>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Dairy &amp; Milk Products</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Cheese &amp; Paneer</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>Moisture Content:%:0:60.0:250; Fat on Dry Basis:%:45.0:70.0:300</t>
         </is>
@@ -1129,54 +1163,60 @@
           <t>Microbial Safety Screen (E. Coli &amp; Coliforms)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>48 Hours</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Microbiology</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>IS:5401 (Part 1):2012 / ISO 4832:2006</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Quantitative enumeration of total viable coliforms and Escherichia coli in food &amp; water matrices.</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>IS:5401 (Part 1):2012 / ISO 4832:2006</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Microbiology</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>48 Hours</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr"/>
+      <c r="O6" s="9" t="inlineStr"/>
+      <c r="P6" s="9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
+      <c r="Q6" s="9" t="inlineStr">
         <is>
           <t>Total Coliform Count:cfu/g:0:10:350; E. Coli Count:cfu/g:0:0:450</t>
         </is>
@@ -1188,53 +1228,60 @@
           <t>Heavy Metals Residue Panel</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>72 Hours</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Chemical</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>AOAC 2015.01 / FSSAI Manual 02</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Inductively Coupled Plasma Mass Spectrometry (ICP-MS) detection for toxic heavy metals.</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>AOAC 2015.01 / FSSAI Manual 02</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>72 Hours</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr"/>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr"/>
+      <c r="O7" s="9" t="inlineStr"/>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>FLAT</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>Lead (Pb):ppm:0.0:0.1:400; Cadmium (Cd):ppm:0.0:0.05:400; Arsenic (As):ppm:0.0:0.1:450; Mercury (Hg):ppm:0.0:0.01:450</t>
         </is>
@@ -1242,7 +1289,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
